--- a/WorkBot/refactor/data/orders/Ithaca Bakery/Ithaca Bakery_Downtown_2025-10-10.xlsx
+++ b/WorkBot/refactor/data/orders/Ithaca Bakery/Ithaca Bakery_Downtown_2025-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1079,14 +1079,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Caramel Apple Butter</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Monin - Caramel Apple Butter</t>
+          <t>Peanut Butter - Creamy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1096,12 +1092,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1105,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Monin - Caramel Sugar Free</t>
+          <t>Register Tape - Thermal (3.125" x 230')</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1119,12 +1115,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>49.99</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>49.99</t>
         </is>
       </c>
     </row>
@@ -1132,22 +1128,22 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Monin - Cookie Butter</t>
+          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>26.01</t>
+          <t>6.96</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1151,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Monin - Guava Puree</t>
+          <t>Tea Bags - English Breakfast (Twinings)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1165,24 +1161,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>29.50</t>
+          <t>9.18</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>WEBSTAURANT</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Monin - Hazelnut</t>
+          <t>Tea Bags - Irish Breakfast (Twinings)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1192,20 +1184,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>3.48</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Web/EC</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Monin - Toffee Nut</t>
+          <t>Torani - Caramel Sauce</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1215,104 +1211,120 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Web/EC</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Monin - Vanilla Sugar Free</t>
+          <t>Torani - Dark Chocolate Sauce</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Peanut Butter - Creamy</t>
+          <t>Torani - Pumpkin Pie Sauce</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>17.40</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>17.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>H&amp;M</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Wrap - Foil (9" x 10.75")</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Register Tape - Thermal (3.125" x 230')</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>49.99</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>49.99</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>H&amp;M</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
+          <t>Wrap - Paper (15" x 10.75")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>5.97</t>
         </is>
       </c>
     </row>
@@ -1320,201 +1332,20 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tea Bags - English Breakfast (Twinings)</t>
+          <t>Lucky 7 Neutral Floor Cleaner</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
-        <is>
-          <t>9.18</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Tea Bags - Irish Breakfast (Twinings)</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Web/EC</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Torani - Caramel Sauce</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Web/EC</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Torani - Dark Chocolate Sauce</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Torani - Pumpkin Pie Sauce</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>17.40</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>17.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>H&amp;M</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Wrap - Foil (9" x 10.75")</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>H&amp;M</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Wrap - Paper (15" x 10.75")</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>5.97</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>5.97</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Lucky 7 Neutral Floor Cleaner</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
         <is>
           <t>12.55</t>
         </is>
